--- a/etf_holdings/2026-10-14_00991A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-14_00991A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:29</t>
+          <t>2026-10-14 00:25:02</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:29</t>
+          <t>2026-10-14 00:25:02</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:29</t>
+          <t>2026-10-14 00:25:02</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:29</t>
+          <t>2026-10-14 00:25:02</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:29</t>
+          <t>2026-10-14 00:25:02</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:29</t>
+          <t>2026-10-14 00:25:02</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:29</t>
+          <t>2026-10-14 00:25:02</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:29</t>
+          <t>2026-10-14 00:25:02</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:29</t>
+          <t>2026-10-14 00:25:02</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:29</t>
+          <t>2026-10-14 00:25:02</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:29</t>
+          <t>2026-10-14 00:25:02</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:29</t>
+          <t>2026-10-14 00:25:02</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:29</t>
+          <t>2026-10-14 00:25:02</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:29</t>
+          <t>2026-10-14 00:25:02</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:29</t>
+          <t>2026-10-14 00:25:02</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:31</t>
+          <t>2026-10-14 00:25:03</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:31</t>
+          <t>2026-10-14 00:25:03</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:31</t>
+          <t>2026-10-14 00:25:03</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:31</t>
+          <t>2026-10-14 00:25:03</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:31</t>
+          <t>2026-10-14 00:25:03</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:31</t>
+          <t>2026-10-14 00:25:03</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:31</t>
+          <t>2026-10-14 00:25:03</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:31</t>
+          <t>2026-10-14 00:25:03</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:31</t>
+          <t>2026-10-14 00:25:03</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:31</t>
+          <t>2026-10-14 00:25:03</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:31</t>
+          <t>2026-10-14 00:25:03</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:31</t>
+          <t>2026-10-14 00:25:03</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:31</t>
+          <t>2026-10-14 00:25:03</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:31</t>
+          <t>2026-10-14 00:25:03</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:31</t>
+          <t>2026-10-14 00:25:03</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:32</t>
+          <t>2026-10-14 00:25:04</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:32</t>
+          <t>2026-10-14 00:25:04</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:32</t>
+          <t>2026-10-14 00:25:04</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:32</t>
+          <t>2026-10-14 00:25:04</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:32</t>
+          <t>2026-10-14 00:25:04</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:32</t>
+          <t>2026-10-14 00:25:04</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:32</t>
+          <t>2026-10-14 00:25:04</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:32</t>
+          <t>2026-10-14 00:25:04</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:32</t>
+          <t>2026-10-14 00:25:04</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:32</t>
+          <t>2026-10-14 00:25:04</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:32</t>
+          <t>2026-10-14 00:25:04</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:32</t>
+          <t>2026-10-14 00:25:04</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:32</t>
+          <t>2026-10-14 00:25:04</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:32</t>
+          <t>2026-10-14 00:25:04</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:32</t>
+          <t>2026-10-14 00:25:04</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:33</t>
+          <t>2026-10-14 00:25:05</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:33</t>
+          <t>2026-10-14 00:25:05</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:33</t>
+          <t>2026-10-14 00:25:05</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:33</t>
+          <t>2026-10-14 00:25:05</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-14 00:08:33</t>
+          <t>2026-10-14 00:25:05</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-10-14_00991A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-14_00991A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:02</t>
+          <t>2026-10-14 21:53:15</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,12 +509,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-1.97%2490</t>
+          <t>0%2490</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-1.97%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -522,12 +522,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>14.03%4,200,000</t>
+          <t>13.95%4,200,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>14.03%</t>
+          <t>13.95%</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -535,7 +535,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-0.27%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:02</t>
+          <t>2026-10-14 21:53:15</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -570,25 +570,25 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-9.84%5545</t>
+          <t>-0.45%5520</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-9.84%</t>
+          <t>-0.45%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>5545</v>
+        <v>5520</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>10.04%1,350,000</t>
+          <t>9.94%1,350,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>10.04%</t>
+          <t>9.94%</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -596,7 +596,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-1.05%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:02</t>
+          <t>2026-10-14 21:53:15</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,25 +631,25 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-5.98%1180</t>
+          <t>+0.42%1185</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-5.98%</t>
+          <t>+0.42%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1180</v>
+        <v>1185</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>8.47%5,350,000</t>
+          <t>8.45%5,350,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>8.47%</t>
+          <t>8.45%</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -657,7 +657,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-0.52%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:02</t>
+          <t>2026-10-14 21:53:15</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -692,25 +692,25 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-7.4%488</t>
+          <t>-1.54%480.5</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-7.4%</t>
+          <t>-1.54%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>488</v>
+        <v>480.5</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>7.66%11,700,000</t>
+          <t>7.50%11,700,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>7.66%</t>
+          <t>7.50%</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -718,7 +718,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-0.59%</t>
+          <t>-0.12%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:02</t>
+          <t>2026-10-14 21:53:15</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -753,25 +753,25 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0%1440</t>
+          <t>-0.69%1430</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-0.69%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>1440</v>
+        <v>1430</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>6.57%3,400,000</t>
+          <t>6.48%3,400,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>6.57%</t>
+          <t>6.48%</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -779,7 +779,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:02</t>
+          <t>2026-10-14 21:53:15</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -814,25 +814,25 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-1.89%1040</t>
+          <t>+0.96%1050</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-1.89%</t>
+          <t>+0.96%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>1040</v>
+        <v>1050</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>6.45%4,620,000</t>
+          <t>6.47%4,620,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>6.45%</t>
+          <t>6.47%</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -840,7 +840,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-0.12%</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:02</t>
+          <t>2026-10-14 21:53:15</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -870,38 +870,38 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2454聯發科</t>
+          <t>2059川湖</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-2.16%4525</t>
+          <t>-0.55%10005</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-2.16%</t>
+          <t>-0.55%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>4525</v>
+        <v>10005</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>6.38%1,050,000</t>
+          <t>6.27%470,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>6.38%</t>
+          <t>6.27%</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>1050000</v>
+        <v>470000</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-0.14%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:02</t>
+          <t>2026-10-14 21:53:15</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -931,38 +931,38 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2059川湖</t>
+          <t>2454聯發科</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-4.91%10060</t>
+          <t>-1.1%4475</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-4.91%</t>
+          <t>-1.1%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>10060</v>
+        <v>4475</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>6.34%470,000</t>
+          <t>6.27%1,050,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>6.34%</t>
+          <t>6.27%</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>470000</v>
+        <v>1050000</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-0.32%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:02</t>
+          <t>2026-10-14 21:53:15</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -997,25 +997,25 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-3.1%3280</t>
+          <t>+1.07%3315</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-3.1%</t>
+          <t>+1.07%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>3280</v>
+        <v>3315</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>5.50%1,250,000</t>
+          <t>5.53%1,250,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>5.50%</t>
+          <t>5.53%</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-0.17%</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:02</t>
+          <t>2026-10-14 21:53:15</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1058,25 +1058,25 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-5.82%599</t>
+          <t>+4.67%627</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-5.82%</t>
+          <t>+4.67%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>599</v>
+        <v>627</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>4.66%5,800,000</t>
+          <t>4.85%5,800,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>4.66%</t>
+          <t>4.85%</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-0.28%</t>
+          <t>+0.22%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:02</t>
+          <t>2026-10-14 21:53:15</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1119,25 +1119,25 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>+5.28%319</t>
+          <t>+9.4%349</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>+5.28%</t>
+          <t>+9.4%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>319</v>
+        <v>349</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3.72%8,700,000</t>
+          <t>4.05%8,700,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>3.72%</t>
+          <t>4.05%</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>+0.18%</t>
+          <t>+0.35%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:02</t>
+          <t>2026-10-14 21:53:15</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1180,25 +1180,25 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-3.52%2195</t>
+          <t>-3.64%2115</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-3.52%</t>
+          <t>-3.64%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>2195</v>
+        <v>2115</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3.39%1,150,020</t>
+          <t>3.24%1,150,020</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>3.39%</t>
+          <t>3.24%</t>
         </is>
       </c>
       <c r="K13" t="n">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:02</t>
+          <t>2026-10-14 21:53:15</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1241,25 +1241,25 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-9.92%2725</t>
+          <t>+5.69%2880</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-9.92%</t>
+          <t>+5.69%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>2725</v>
+        <v>2880</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2.92%800,000</t>
+          <t>3.07%800,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2.92%</t>
+          <t>3.07%</t>
         </is>
       </c>
       <c r="K14" t="n">
@@ -1267,7 +1267,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-0.31%</t>
+          <t>+0.17%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:02</t>
+          <t>2026-10-14 21:53:15</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1302,25 +1302,25 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-4.05%806</t>
+          <t>+5.96%854</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-4.05%</t>
+          <t>+5.96%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>806</v>
+        <v>854</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2.81%2,600,000</t>
+          <t>2.96%2,600,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2.81%</t>
+          <t>2.96%</t>
         </is>
       </c>
       <c r="K15" t="n">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-0.11%</t>
+          <t>+0.17%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:02</t>
+          <t>2026-10-14 21:53:15</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1363,25 +1363,25 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-2.37%6990</t>
+          <t>+1.14%7070</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-2.37%</t>
+          <t>+1.14%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>6990</v>
+        <v>7070</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2.72%290,000</t>
+          <t>2.73%290,000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2.72%</t>
+          <t>2.73%</t>
         </is>
       </c>
       <c r="K16" t="n">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:03</t>
+          <t>2026-10-14 21:53:17</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1424,25 +1424,25 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-1.95%17350</t>
+          <t>+0.86%17500</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-1.95%</t>
+          <t>+0.86%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>17350</v>
+        <v>17500</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.57%110,500</t>
+          <t>2.58%110,500</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2.57%</t>
+          <t>2.58%</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:03</t>
+          <t>2026-10-14 21:53:17</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1485,16 +1485,16 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-2.89%740</t>
+          <t>+0.95%747</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-2.89%</t>
+          <t>+0.95%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>740</v>
+        <v>747</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:03</t>
+          <t>2026-10-14 21:53:17</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1546,25 +1546,25 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>+9.68%119</t>
+          <t>+0.42%119.5</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>+9.68%</t>
+          <t>+0.42%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>119</v>
+        <v>119.5</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.60%10,000,000</t>
+          <t>1.59%10,000,000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>1.60%</t>
+          <t>1.59%</t>
         </is>
       </c>
       <c r="K19" t="n">
@@ -1572,7 +1572,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>+0.14%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:03</t>
+          <t>2026-10-14 21:53:17</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1607,33 +1607,33 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-0.68%7275</t>
+          <t>-5.43%6880</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-0.68%</t>
+          <t>-5.43%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>7275</v>
+        <v>6880</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.07%110,000</t>
+          <t>1.19%130,000</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.07%</t>
+          <t>1.19%</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>110000</v>
+        <v>130000</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:03</t>
+          <t>2026-10-14 21:53:17</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1663,21 +1663,21 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>7769鴻勁</t>
+          <t>6223旺矽</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-6.47%6070</t>
+          <t>-0.93%5885</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-6.47%</t>
+          <t>-0.93%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>6070</v>
+        <v>5885</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:03</t>
+          <t>2026-10-14 21:53:17</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1724,21 +1724,21 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>6223旺矽</t>
+          <t>7769鴻勁</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-3.1%5940</t>
+          <t>-4.78%5780</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-3.1%</t>
+          <t>-4.78%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>5940</v>
+        <v>5780</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:03</t>
+          <t>2026-10-14 21:53:17</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1790,12 +1790,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>+0.31%323</t>
+          <t>0%323</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>+0.31%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H23" t="n">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:03</t>
+          <t>2026-10-14 21:53:17</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1851,16 +1851,16 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>+3.33%264</t>
+          <t>-0.38%263</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>+3.33%</t>
+          <t>-0.38%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1877,7 +1877,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:03</t>
+          <t>2026-10-14 21:53:17</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1907,21 +1907,21 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>3665貿聯-KY</t>
+          <t>2360致茂</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-4.03%2260</t>
+          <t>+2.27%2250</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-4.03%</t>
+          <t>+2.27%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>2260</v>
+        <v>2250</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1938,7 +1938,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:03</t>
+          <t>2026-10-14 21:53:17</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1968,25 +1968,25 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2360致茂</t>
+          <t>2317鴻海</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-6.98%2200</t>
+          <t>+1.25%243</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-6.98%</t>
+          <t>+1.25%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>2200</v>
+        <v>243</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>&lt;0.01%1,000</t>
+          <t>&lt;0.01%9,000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -1995,11 +1995,11 @@
         </is>
       </c>
       <c r="K26" t="n">
-        <v>1000</v>
+        <v>9000</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:03</t>
+          <t>2026-10-14 21:53:17</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2029,25 +2029,25 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2317鴻海</t>
+          <t>3665貿聯-KY</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-1.84%240</t>
+          <t>-1.11%2235</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-1.84%</t>
+          <t>-1.11%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>240</v>
+        <v>2235</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>&lt;0.01%9,000</t>
+          <t>&lt;0.01%1,000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2056,7 +2056,7 @@
         </is>
       </c>
       <c r="K27" t="n">
-        <v>9000</v>
+        <v>1000</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:03</t>
+          <t>2026-10-14 21:53:17</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2095,16 +2095,16 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-4.23%2040</t>
+          <t>+0.49%2050</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-4.23%</t>
+          <t>+0.49%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>2040</v>
+        <v>2050</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:03</t>
+          <t>2026-10-14 21:53:17</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2156,12 +2156,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-4.38%1965</t>
+          <t>0%1965</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-4.38%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H29" t="n">
@@ -2182,7 +2182,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:03</t>
+          <t>2026-10-14 21:53:17</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2212,21 +2212,21 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2308台達電</t>
+          <t>6274台燿</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-6.58%1775</t>
+          <t>+4.83%1735</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-6.58%</t>
+          <t>+4.83%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>1775</v>
+        <v>1735</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:03</t>
+          <t>2026-10-14 21:53:17</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2273,21 +2273,21 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>6274台燿</t>
+          <t>2308台達電</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>-4.61%1655</t>
+          <t>+0.56%1785</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-4.61%</t>
+          <t>+0.56%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>1655</v>
+        <v>1785</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:04</t>
+          <t>2026-10-14 21:53:18</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>-1.32%187</t>
+          <t>0%187</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-1.32%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H32" t="n">
@@ -2365,7 +2365,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:04</t>
+          <t>2026-10-14 21:53:18</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2400,16 +2400,16 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>-3.31%175</t>
+          <t>+0.57%176</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-3.31%</t>
+          <t>+0.57%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -2426,7 +2426,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:04</t>
+          <t>2026-10-14 21:53:18</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2461,16 +2461,16 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>+0.95%160</t>
+          <t>+0.31%160.5</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>+0.95%</t>
+          <t>+0.31%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>160</v>
+        <v>160.5</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:04</t>
+          <t>2026-10-14 21:53:18</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2522,16 +2522,16 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>-2.75%141.5</t>
+          <t>+0.35%142</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-2.75%</t>
+          <t>+0.35%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>141.5</v>
+        <v>142</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:04</t>
+          <t>2026-10-14 21:53:18</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2578,25 +2578,25 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2882國泰金</t>
+          <t>2357華碩</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>+1.33%114.5</t>
+          <t>+2.48%990</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>+1.33%</t>
+          <t>+2.48%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>114.5</v>
+        <v>990</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>&lt;0.01%9,000</t>
+          <t>&lt;0.01%1,000</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2605,7 +2605,7 @@
         </is>
       </c>
       <c r="K36" t="n">
-        <v>9000</v>
+        <v>1000</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:04</t>
+          <t>2026-10-14 21:53:18</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2639,25 +2639,25 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2357華碩</t>
+          <t>2882國泰金</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>-1.13%966</t>
+          <t>-0.44%114</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-1.13%</t>
+          <t>-0.44%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>966</v>
+        <v>114</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>&lt;0.01%1,000</t>
+          <t>&lt;0.01%9,000</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2666,7 +2666,7 @@
         </is>
       </c>
       <c r="K37" t="n">
-        <v>1000</v>
+        <v>9000</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:04</t>
+          <t>2026-10-14 21:53:18</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2705,16 +2705,16 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>+1.61%758</t>
+          <t>+2.64%778</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>+1.61%</t>
+          <t>+2.64%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>758</v>
+        <v>778</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:04</t>
+          <t>2026-10-14 21:53:18</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2766,16 +2766,16 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>+0.71%70.6</t>
+          <t>+2.27%72.2</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>+0.71%</t>
+          <t>+2.27%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>70.59999999999999</v>
+        <v>72.2</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:04</t>
+          <t>2026-10-14 21:53:18</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2827,16 +2827,16 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>+2.58%71.6</t>
+          <t>-0.28%71.4</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>+2.58%</t>
+          <t>-0.28%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>71.59999999999999</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -2853,7 +2853,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:04</t>
+          <t>2026-10-14 21:53:18</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2888,16 +2888,16 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>-1.21%572</t>
+          <t>+5.42%603</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-1.21%</t>
+          <t>+5.42%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>572</v>
+        <v>603</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:04</t>
+          <t>2026-10-14 21:53:18</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2949,16 +2949,16 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>+1.8%50.9</t>
+          <t>+0.39%51.1</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>+1.8%</t>
+          <t>+0.39%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>50.9</v>
+        <v>51.1</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:04</t>
+          <t>2026-10-14 21:53:18</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3005,25 +3005,25 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2880華南金</t>
+          <t>2887台新新光金</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>+3.57%49.35</t>
+          <t>-0.81%42.65</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>+3.57%</t>
+          <t>-0.81%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>49.35</v>
+        <v>42.65</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>&lt;0.01%9,090</t>
+          <t>&lt;0.01%9,000</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3032,11 +3032,11 @@
         </is>
       </c>
       <c r="K43" t="n">
-        <v>9090</v>
+        <v>9000</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:04</t>
+          <t>2026-10-14 21:53:18</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3066,21 +3066,21 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2887台新新光金</t>
+          <t>2890永豐金</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>0%43</t>
+          <t>-1.56%44.05</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-1.56%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>43</v>
+        <v>44.05</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -3097,7 +3097,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:04</t>
+          <t>2026-10-14 21:53:18</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3127,25 +3127,25 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2890永豐金</t>
+          <t>2880華南金</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>-1%44.75</t>
+          <t>-0.91%48.9</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-1%</t>
+          <t>-0.91%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>44.75</v>
+        <v>48.9</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>&lt;0.01%9,000</t>
+          <t>&lt;0.01%9,090</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3154,7 +3154,7 @@
         </is>
       </c>
       <c r="K45" t="n">
-        <v>9000</v>
+        <v>9090</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:04</t>
+          <t>2026-10-14 21:53:18</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3193,16 +3193,16 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>+1.67%305</t>
+          <t>-2.79%296.5</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>+1.67%</t>
+          <t>-2.79%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>305</v>
+        <v>296.5</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -3219,7 +3219,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:05</t>
+          <t>2026-10-14 21:53:19</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3254,16 +3254,16 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>+1.09%46.5</t>
+          <t>+1.72%47.3</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>+1.09%</t>
+          <t>+1.72%</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>46.5</v>
+        <v>47.3</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:05</t>
+          <t>2026-10-14 21:53:19</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3315,16 +3315,16 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>-0.13%38.75</t>
+          <t>-0.26%38.65</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-0.13%</t>
+          <t>-0.26%</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>38.75</v>
+        <v>38.65</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:05</t>
+          <t>2026-10-14 21:53:19</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3376,16 +3376,16 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>-3.37%243.5</t>
+          <t>+2.87%250.5</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-3.37%</t>
+          <t>+2.87%</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>243.5</v>
+        <v>250.5</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:05</t>
+          <t>2026-10-14 21:53:19</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3437,16 +3437,16 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>-2.31%211.5</t>
+          <t>+2.13%216</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-2.31%</t>
+          <t>+2.13%</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>211.5</v>
+        <v>216</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-14 00:25:05</t>
+          <t>2026-10-14 21:53:19</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3498,16 +3498,16 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>+1.02%148</t>
+          <t>+0.34%148.5</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>+1.02%</t>
+          <t>+0.34%</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>148</v>
+        <v>148.5</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>

--- a/etf_holdings/2026-10-14_00991A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-14_00991A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:15</t>
+          <t>2026-10-14 22:00:59</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:15</t>
+          <t>2026-10-14 22:00:59</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:15</t>
+          <t>2026-10-14 22:00:59</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:15</t>
+          <t>2026-10-14 22:00:59</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:15</t>
+          <t>2026-10-14 22:00:59</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:15</t>
+          <t>2026-10-14 22:00:59</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:15</t>
+          <t>2026-10-14 22:00:59</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:15</t>
+          <t>2026-10-14 22:00:59</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:15</t>
+          <t>2026-10-14 22:00:59</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:15</t>
+          <t>2026-10-14 22:00:59</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:15</t>
+          <t>2026-10-14 22:00:59</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:15</t>
+          <t>2026-10-14 22:00:59</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:15</t>
+          <t>2026-10-14 22:00:59</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:15</t>
+          <t>2026-10-14 22:00:59</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:15</t>
+          <t>2026-10-14 22:00:59</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:17</t>
+          <t>2026-10-14 22:01:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:17</t>
+          <t>2026-10-14 22:01:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:17</t>
+          <t>2026-10-14 22:01:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:17</t>
+          <t>2026-10-14 22:01:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:17</t>
+          <t>2026-10-14 22:01:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:17</t>
+          <t>2026-10-14 22:01:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:17</t>
+          <t>2026-10-14 22:01:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:17</t>
+          <t>2026-10-14 22:01:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:17</t>
+          <t>2026-10-14 22:01:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:17</t>
+          <t>2026-10-14 22:01:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:17</t>
+          <t>2026-10-14 22:01:00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:17</t>
+          <t>2026-10-14 22:01:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:17</t>
+          <t>2026-10-14 22:01:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:17</t>
+          <t>2026-10-14 22:01:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:17</t>
+          <t>2026-10-14 22:01:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:18</t>
+          <t>2026-10-14 22:01:01</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:18</t>
+          <t>2026-10-14 22:01:01</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:18</t>
+          <t>2026-10-14 22:01:01</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:18</t>
+          <t>2026-10-14 22:01:01</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:18</t>
+          <t>2026-10-14 22:01:01</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:18</t>
+          <t>2026-10-14 22:01:01</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:18</t>
+          <t>2026-10-14 22:01:01</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:18</t>
+          <t>2026-10-14 22:01:01</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:18</t>
+          <t>2026-10-14 22:01:01</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:18</t>
+          <t>2026-10-14 22:01:01</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:18</t>
+          <t>2026-10-14 22:01:01</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:18</t>
+          <t>2026-10-14 22:01:01</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:18</t>
+          <t>2026-10-14 22:01:01</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:18</t>
+          <t>2026-10-14 22:01:01</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:18</t>
+          <t>2026-10-14 22:01:01</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:19</t>
+          <t>2026-10-14 22:01:03</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:19</t>
+          <t>2026-10-14 22:01:03</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:19</t>
+          <t>2026-10-14 22:01:03</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:19</t>
+          <t>2026-10-14 22:01:03</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-14 21:53:19</t>
+          <t>2026-10-14 22:01:03</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-10-14_00991A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-14_00991A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-14 22:00:59</t>
+          <t>2026-10-14 22:31:01</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-14 22:00:59</t>
+          <t>2026-10-14 22:31:01</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-14 22:00:59</t>
+          <t>2026-10-14 22:31:01</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-14 22:00:59</t>
+          <t>2026-10-14 22:31:01</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-14 22:00:59</t>
+          <t>2026-10-14 22:31:01</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-14 22:00:59</t>
+          <t>2026-10-14 22:31:01</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-14 22:00:59</t>
+          <t>2026-10-14 22:31:01</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-14 22:00:59</t>
+          <t>2026-10-14 22:31:01</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-14 22:00:59</t>
+          <t>2026-10-14 22:31:01</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-14 22:00:59</t>
+          <t>2026-10-14 22:31:01</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-14 22:00:59</t>
+          <t>2026-10-14 22:31:01</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-14 22:00:59</t>
+          <t>2026-10-14 22:31:01</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-14 22:00:59</t>
+          <t>2026-10-14 22:31:01</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-14 22:00:59</t>
+          <t>2026-10-14 22:31:01</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-14 22:00:59</t>
+          <t>2026-10-14 22:31:01</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:00</t>
+          <t>2026-10-14 22:31:03</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:00</t>
+          <t>2026-10-14 22:31:03</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:00</t>
+          <t>2026-10-14 22:31:03</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:00</t>
+          <t>2026-10-14 22:31:03</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:00</t>
+          <t>2026-10-14 22:31:03</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:00</t>
+          <t>2026-10-14 22:31:03</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:00</t>
+          <t>2026-10-14 22:31:03</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:00</t>
+          <t>2026-10-14 22:31:03</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:00</t>
+          <t>2026-10-14 22:31:03</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:00</t>
+          <t>2026-10-14 22:31:03</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:00</t>
+          <t>2026-10-14 22:31:03</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:00</t>
+          <t>2026-10-14 22:31:03</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:00</t>
+          <t>2026-10-14 22:31:03</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:00</t>
+          <t>2026-10-14 22:31:03</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:00</t>
+          <t>2026-10-14 22:31:03</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:01</t>
+          <t>2026-10-14 22:31:04</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:01</t>
+          <t>2026-10-14 22:31:04</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:01</t>
+          <t>2026-10-14 22:31:04</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:01</t>
+          <t>2026-10-14 22:31:04</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:01</t>
+          <t>2026-10-14 22:31:04</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:01</t>
+          <t>2026-10-14 22:31:04</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:01</t>
+          <t>2026-10-14 22:31:04</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:01</t>
+          <t>2026-10-14 22:31:04</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:01</t>
+          <t>2026-10-14 22:31:04</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:01</t>
+          <t>2026-10-14 22:31:04</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:01</t>
+          <t>2026-10-14 22:31:04</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:01</t>
+          <t>2026-10-14 22:31:04</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:01</t>
+          <t>2026-10-14 22:31:04</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:01</t>
+          <t>2026-10-14 22:31:04</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:01</t>
+          <t>2026-10-14 22:31:04</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:03</t>
+          <t>2026-10-14 22:31:05</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:03</t>
+          <t>2026-10-14 22:31:05</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:03</t>
+          <t>2026-10-14 22:31:05</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:03</t>
+          <t>2026-10-14 22:31:05</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-14 22:01:03</t>
+          <t>2026-10-14 22:31:05</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
